--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N67_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N67_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.62939218503624</v>
+        <v>9.202276230068389</v>
       </c>
       <c r="D2" t="n">
-        <v>10.32405994991187</v>
+        <v>1.677659741860679</v>
       </c>
       <c r="E2" t="n">
-        <v>19.32406713768554</v>
+        <v>3.140160909873901</v>
       </c>
       <c r="F2" t="n">
-        <v>5.022993942901276</v>
+        <v>0.8162365157214573</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.85419177830148</v>
+        <v>11.02630616397399</v>
       </c>
       <c r="D3" t="n">
-        <v>21.10718391825184</v>
+        <v>3.429917386715924</v>
       </c>
       <c r="E3" t="n">
-        <v>19.32406713768554</v>
+        <v>3.140160909873901</v>
       </c>
       <c r="F3" t="n">
-        <v>5.022993942901276</v>
+        <v>0.8162365157214573</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.41854532966575</v>
+        <v>3.643013616070685</v>
       </c>
       <c r="D4" t="n">
-        <v>10.58431753953829</v>
+        <v>1.719951600174972</v>
       </c>
       <c r="E4" t="n">
-        <v>19.32406713768554</v>
+        <v>3.140160909873901</v>
       </c>
       <c r="F4" t="n">
-        <v>5.022993942901276</v>
+        <v>0.8162365157214573</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
